--- a/Configs/GameConfig/Datas/fg/#RaidDifficulty-突袭难度.xlsx
+++ b/Configs/GameConfig/Datas/fg/#RaidDifficulty-突袭难度.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,41 @@
           <t>nameKey</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>enemyHp</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>enemyDamage</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>silentNightDays</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>eventRate</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>descKey</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>sortOrder</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +524,41 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +594,41 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>难度名称文本键</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>敌人耐久倍率(突袭部队展开成战斗单位时乘到生命上;FG16 第 3 节“敌人耐久和伤害”)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>敌人伤害倍率(突袭部队展开时乘到武器伤害上)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>静默夜间隔(游戏日;静默夜系统 FG7-ENV-02 读取)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>事件频率倍率(事件导演 FG12-EVT-01 读取;FG16“少 / 标准 / 多”)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>难度一句话说明文本键(新游戏 / 难度面板)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1=自定义:突袭频率 / 规模 / 预警由玩家用滑条设定(存档 RaidDifficultyState),本行三个倍率是滑条初值</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>界面上的顺序</t>
         </is>
       </c>
     </row>
@@ -551,6 +656,29 @@
           <t>difficulty.builder.name</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>difficulty.builder.desc</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -576,6 +704,29 @@
           <t>difficulty.standard.name</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>difficulty.standard.desc</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -600,6 +751,77 @@
         <is>
           <t>difficulty.harsh.name</t>
         </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>difficulty.harsh.desc</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>difficulty.custom.name</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>difficulty.custom.desc</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
